--- a/output/tables/Table3_Predictors_by_SNAP.xlsx
+++ b/output/tables/Table3_Predictors_by_SNAP.xlsx
@@ -42,22 +42,22 @@
     <t>0.03</t>
   </si>
   <si>
-    <t>-0.06 (-0.09, -0.02)</t>
-  </si>
-  <si>
-    <t>0.002</t>
+    <t>-0.05 (-0.09, -0.02)</t>
+  </si>
+  <si>
+    <t>0.003</t>
   </si>
   <si>
     <t>-0.00 (-0.04, 0.04)</t>
   </si>
   <si>
-    <t>0.97</t>
+    <t>0.95</t>
   </si>
   <si>
     <t>Perceived health risk of soda</t>
   </si>
   <si>
-    <t>0.007</t>
+    <t>0.006</t>
   </si>
   <si>
     <t>0.18 (0.13, 0.23)</t>
@@ -66,7 +66,7 @@
     <t>&lt;0.001</t>
   </si>
   <si>
-    <t>0.25 (0.22, 0.29)</t>
+    <t>0.26 (0.22, 0.29)</t>
   </si>
   <si>
     <t>Embarrassment when paying with SNAP</t>

--- a/output/tables/Table3_Predictors_by_SNAP.xlsx
+++ b/output/tables/Table3_Predictors_by_SNAP.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="36">
   <si>
     <t>Table 3. Associations of psychological predictors with support for SNAP soft-drink/candy restrictions, by SNAP participation (N = 8715)</t>
   </si>
@@ -36,6 +36,9 @@
     <t>p</t>
   </si>
   <si>
+    <t>Cohen's d</t>
+  </si>
+  <si>
     <t>Self-reported soda overconsumption</t>
   </si>
   <si>
@@ -48,12 +51,18 @@
     <t>0.003</t>
   </si>
   <si>
+    <t>-0.04</t>
+  </si>
+  <si>
     <t>-0.00 (-0.04, 0.04)</t>
   </si>
   <si>
     <t>0.95</t>
   </si>
   <si>
+    <t>-0.00</t>
+  </si>
+  <si>
     <t>Perceived health risk of soda</t>
   </si>
   <si>
@@ -66,34 +75,52 @@
     <t>&lt;0.001</t>
   </si>
   <si>
+    <t>0.12</t>
+  </si>
+  <si>
     <t>0.26 (0.22, 0.29)</t>
   </si>
   <si>
+    <t>0.18</t>
+  </si>
+  <si>
     <t>Embarrassment when paying with SNAP</t>
   </si>
   <si>
     <t>-0.11 (-0.14, -0.08)</t>
   </si>
   <si>
+    <t>-0.07</t>
+  </si>
+  <si>
     <t>0.01 (-0.03, 0.05)</t>
   </si>
   <si>
     <t>0.77</t>
   </si>
   <si>
+    <t>0.00</t>
+  </si>
+  <si>
     <t>Perceived stigma of SNAP policies</t>
   </si>
   <si>
     <t>-0.45 (-0.52, -0.39)</t>
   </si>
   <si>
+    <t>-0.31</t>
+  </si>
+  <si>
     <t>-0.12 (-0.22, -0.03)</t>
   </si>
   <si>
     <t>0.01</t>
   </si>
   <si>
-    <t>Note. Coefficients are simple slopes (change in support per 1-unit increase in the predictor) from an OLS model with continuous predictors, SNAP participation, predictor×SNAP interactions, and covariates (age, gender, ethnicity, education, income, census region, children in household, state restriction status). Standard errors clustered by state. Outcome: support for removing soft drinks and candy from SNAP-eligible purchases (1 = Strongly oppose to 5 = Strongly support). Unweighted. Complete-case analysis.</t>
+    <t>-0.08</t>
+  </si>
+  <si>
+    <t>Note. Coefficients are simple slopes (change in support per 1-unit increase in the predictor) from an OLS model with continuous predictors, SNAP participation, predictor×SNAP interactions, and covariates (age, gender, ethnicity, education, income, census region, children in household, state restriction status). Cohen's d = b / SD(support), the change in support in outcome SD units per 1-unit increase in the predictor. Standard errors clustered by state. Outcome: support for removing soft drinks and candy from SNAP-eligible purchases (1 = Strongly oppose to 5 = Strongly support). Unweighted. Complete-case analysis.</t>
   </si>
 </sst>
 </file>
@@ -137,7 +164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -152,10 +179,10 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -167,95 +194,125 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
         <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/Table3_Predictors_by_SNAP.xlsx
+++ b/output/tables/Table3_Predictors_by_SNAP.xlsx
@@ -33,12 +33,12 @@
     <t>b (95% CI)</t>
   </si>
   <si>
+    <t>Cohen's d</t>
+  </si>
+  <si>
     <t>p</t>
   </si>
   <si>
-    <t>Cohen's d</t>
-  </si>
-  <si>
     <t>Self-reported soda overconsumption</t>
   </si>
   <si>
@@ -48,21 +48,21 @@
     <t>-0.05 (-0.09, -0.02)</t>
   </si>
   <si>
+    <t>-0.04</t>
+  </si>
+  <si>
     <t>0.003</t>
   </si>
   <si>
-    <t>-0.04</t>
-  </si>
-  <si>
     <t>-0.00 (-0.04, 0.04)</t>
   </si>
   <si>
+    <t>-0.00</t>
+  </si>
+  <si>
     <t>0.95</t>
   </si>
   <si>
-    <t>-0.00</t>
-  </si>
-  <si>
     <t>Perceived health risk of soda</t>
   </si>
   <si>
@@ -72,12 +72,12 @@
     <t>0.18 (0.13, 0.23)</t>
   </si>
   <si>
+    <t>0.12</t>
+  </si>
+  <si>
     <t>&lt;0.001</t>
   </si>
   <si>
-    <t>0.12</t>
-  </si>
-  <si>
     <t>0.26 (0.22, 0.29)</t>
   </si>
   <si>
@@ -96,12 +96,12 @@
     <t>0.01 (-0.03, 0.05)</t>
   </si>
   <si>
+    <t>0.00</t>
+  </si>
+  <si>
     <t>0.77</t>
   </si>
   <si>
-    <t>0.00</t>
-  </si>
-  <si>
     <t>Perceived stigma of SNAP policies</t>
   </si>
   <si>
@@ -114,10 +114,10 @@
     <t>-0.12 (-0.22, -0.03)</t>
   </si>
   <si>
+    <t>-0.08</t>
+  </si>
+  <si>
     <t>0.01</t>
-  </si>
-  <si>
-    <t>-0.08</t>
   </si>
   <si>
     <t>Note. Coefficients are simple slopes (change in support per 1-unit increase in the predictor) from an OLS model with continuous predictors, SNAP participation, predictor×SNAP interactions, and covariates (age, gender, ethnicity, education, income, census region, children in household, state restriction status). Cohen's d = b / SD(support), the change in support in outcome SD units per 1-unit increase in the predictor. Standard errors clustered by state. Outcome: support for removing soft drinks and candy from SNAP-eligible purchases (1 = Strongly oppose to 5 = Strongly support). Unweighted. Complete-case analysis.</t>
@@ -249,10 +249,10 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -266,10 +266,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
@@ -281,7 +281,7 @@
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -292,10 +292,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
@@ -307,7 +307,7 @@
         <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">

--- a/output/tables/Table3_Predictors_by_SNAP.xlsx
+++ b/output/tables/Table3_Predictors_by_SNAP.xlsx
@@ -72,7 +72,7 @@
     <t>0.18 (0.13, 0.23)</t>
   </si>
   <si>
-    <t>0.12</t>
+    <t>0.13</t>
   </si>
   <si>
     <t>&lt;0.001</t>
@@ -81,7 +81,7 @@
     <t>0.26 (0.22, 0.29)</t>
   </si>
   <si>
-    <t>0.18</t>
+    <t>0.19</t>
   </si>
   <si>
     <t>Embarrassment when paying with SNAP</t>
@@ -90,7 +90,7 @@
     <t>-0.11 (-0.14, -0.08)</t>
   </si>
   <si>
-    <t>-0.07</t>
+    <t>-0.09</t>
   </si>
   <si>
     <t>0.01 (-0.03, 0.05)</t>
@@ -108,19 +108,19 @@
     <t>-0.45 (-0.52, -0.39)</t>
   </si>
   <si>
-    <t>-0.31</t>
+    <t>-0.36</t>
   </si>
   <si>
     <t>-0.12 (-0.22, -0.03)</t>
   </si>
   <si>
-    <t>-0.08</t>
+    <t>-0.10</t>
   </si>
   <si>
     <t>0.01</t>
   </si>
   <si>
-    <t>Note. Coefficients are simple slopes (change in support per 1-unit increase in the predictor) from an OLS model with continuous predictors, SNAP participation, predictor×SNAP interactions, and covariates (age, gender, ethnicity, education, income, census region, children in household, state restriction status). Cohen's d = b / SD(support), the change in support in outcome SD units per 1-unit increase in the predictor. Standard errors clustered by state. Outcome: support for removing soft drinks and candy from SNAP-eligible purchases (1 = Strongly oppose to 5 = Strongly support). Unweighted. Complete-case analysis.</t>
+    <t>Note. Coefficients are simple slopes (change in support per 1-unit increase in the predictor) from an OLS model with continuous predictors, SNAP participation, predictor×SNAP interactions, and covariates (age, gender, ethnicity, education, income, census region, children in household, state restriction status). Cohen's d is the fully standardized effect: b × SD(predictor) / SD(support), using the analysis-sample SD of each predictor (common across SNAP groups) so effects are comparable across predictors and between Non-SNAP and SNAP. Standard errors clustered by state. Outcome: support for removing soft drinks and candy from SNAP-eligible purchases (1 = Strongly oppose to 5 = Strongly support). Unweighted. Complete-case analysis.</t>
   </si>
 </sst>
 </file>
